--- a/Question_Bank_Chapter_Bulk_Upload_Template.xlsx
+++ b/Question_Bank_Chapter_Bulk_Upload_Template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -73,6 +76,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,73 +445,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Parent Chapter No</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Natural numbers, whole numbers, integers and related concepts</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Fractions and Decimals</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Operations on fractions and decimals</t>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Basic arithmetic concepts</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Whole Numbers</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Properties and operations of whole numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Types and operations on fractions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Basic shapes, lines, angles and geometric concepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lines and Angles</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Basic lines and angles</t>
         </is>
       </c>
     </row>
@@ -521,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -529,118 +604,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Question Bank – Bulk Chapter Upload</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Upload many chapter records into the teacher Question Bank.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CHAPTER / SUBCHAPTER BULK UPLOAD — INSTRUCTIONS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Required columns</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Chapter No, Chapter Name</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chapter No</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Use 1, 2, 3 for main chapters and 1.1, 1.2, 2.1 for subchapters.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Optional column</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Parent Chapter No</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Leave blank for a main chapter. For 2.1 use 2; for 2.1.1 use 2.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chapter Name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Chapter No</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Use a positive integer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Chapter Name</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Use the exact chapter name you want displayed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Optional short description or syllabus scope.</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Optional.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Duplicate handling</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>When importing, you can choose Skip duplicates, Update existing chapters, or Stop on duplicate.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Include parent chapters in the same file before their subchapters, or ensure they already exist.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Blank rows</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Blank rows are ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Do not change the header names. Save the file as .xlsx before uploading.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Question Bank</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Questions may be assigned to either a main chapter or a subchapter.</t>
         </is>
       </c>
     </row>

--- a/Question_Bank_Chapter_Bulk_Upload_Template.xlsx
+++ b/Question_Bank_Chapter_Bulk_Upload_Template.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -460,17 +460,22 @@
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Parent Chapter No</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -480,13 +485,17 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Natural numbers, whole numbers, integers and related concepts</t>
         </is>
@@ -496,13 +505,12 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Arithmetic</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Basic arithmetic concepts</t>
         </is>
@@ -514,15 +522,15 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Whole Numbers</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Properties and operations of whole numbers</t>
         </is>
@@ -534,15 +542,15 @@
           <t>2.2</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Fractions</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Types and operations on fractions</t>
         </is>
@@ -552,13 +560,12 @@
       <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Basic shapes, lines, angles and geometric concepts</t>
         </is>
@@ -570,15 +577,15 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Lines and Angles</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Basic lines and angles</t>
         </is>
